--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.80388687391632</v>
+        <v>3.705631617011402</v>
       </c>
       <c r="D2" t="n">
-        <v>22.90344591277377</v>
+        <v>3.721809960825737</v>
       </c>
       <c r="E2" t="n">
-        <v>7.060879412370596</v>
+        <v>1.147392904510222</v>
       </c>
       <c r="F2" t="n">
-        <v>7.061471817839196</v>
+        <v>1.147489170398869</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.70937708654291</v>
+        <v>3.040273776563224</v>
       </c>
       <c r="D3" t="n">
-        <v>18.61483640688448</v>
+        <v>3.024910916118728</v>
       </c>
       <c r="E3" t="n">
-        <v>7.060879412370596</v>
+        <v>1.147392904510222</v>
       </c>
       <c r="F3" t="n">
-        <v>7.061471817839196</v>
+        <v>1.147489170398869</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.30923736699809</v>
+        <v>5.73775107213719</v>
       </c>
       <c r="D4" t="n">
-        <v>35.27105352288846</v>
+        <v>5.731546197469375</v>
       </c>
       <c r="E4" t="n">
-        <v>7.060879412370596</v>
+        <v>1.147392904510222</v>
       </c>
       <c r="F4" t="n">
-        <v>7.061471817839196</v>
+        <v>1.147489170398869</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
